--- a/agriculture 7.xlsx
+++ b/agriculture 7.xlsx
@@ -277,6 +277,9 @@
     <t xml:space="preserve">2021-22</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit:- </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -284,7 +287,6 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source:</t>
     </r>
@@ -294,76 +296,9 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> EPWRF (Economic &amp; Political Weekly Research Foundation) (1950-2021)</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Note:</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Arunachal Pradesh:-&gt; Data for Arunachal Pradesh referred as North-East Frontier Agency (NEFA) for the years 1962-63 To 1969-70.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Chhattisgarh, Jharkhand and Uttarakhand States are available from 2000-01 onwards.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Data of Himachal Pradesh and Punjab States for the years 1962-63 To 1964-65 relates to the set up before 1.11.1966.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:-&gt; Figures for the years 1970-71 onwards relates to new State of Assam (excluding Meghalaya). Earlier data relates to Erstwhile State of Assam.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1966-67 to 1969-70 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Assam:-&gt; Yield has been calculated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1966-67 to 1994-95 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Tamil Nadu:-&gt; Yield has been calculated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1966-67 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Andhra Pradesh:-&gt; Yield has been calculated for the years 1966-67 To 1969-70 and 1992-93 To 1995-96.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1970-71 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Meghalaya:-&gt; Yield has been calculated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1971-72 to 1975-76 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Manipur:-&gt; Yield has been calculated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1971-72 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Tripura:-&gt; Yield has been calculated for the years 1971-72 To 1979-80 and 1986-87 To 1995-96.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1973-74 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Dadra and Nagar Haveli:-&gt; Yield has been calculated for the years 1973-74 To 1979-80 and 1986-87 To 1995-96.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1975-76 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Arunachal Pradesh:-&gt; Yield has been calculated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1981-82 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Sikkim:-&gt; Yield has been calculated for the years 1981-82 To 1984-85, 1994-95 and 1995-96.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1990-91 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Nagaland:-&gt; Yield has been calculated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1992-93 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Odisha:-&gt; Yield has been calculated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016-17 to 2020-21 - Data for the years are Final Estimates as released on 25.05.2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-21 to 2020-21 - : All-India:-&gt; Data for the year 2020-21 are Final Estimates as released on 16.02.2022 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-22 to 2021-22 - : All-India:-&gt; Data for the year 2021-22 are 3rd Advance Estimates as released on 19.05.2022 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The yield rates given for all foodgrains have been worked out on the basis of production &amp; area figures taken in '000 units.</t>
   </si>
   <si>
     <r>
@@ -373,7 +308,87 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Note:- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Arunachal Pradesh:-&gt; Data for Arunachal Pradesh referred as North-East Frontier Agency (NEFA) for the years 1962-63 To 1969-70.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Chhattisgarh, Jharkhand and Uttarakhand States are available from 2000-01 onwards.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Daman and Diu are included under Goa, Daman and Diu for the years 1962-63 To 1979-80.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data for Haryana are included under Punjab for the years 1962-63 To 1964-65.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data of Himachal Pradesh and Punjab States for the years 1962-63 To 1964-65 relates to the set up before 1.11.1966.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Figures for the years 1970-71 onwards relates to new State of Assam (excluding Meghalaya). Earlier data relates to Erstwhile State of Assam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1966-67 to 1969-70 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Assam:-&gt; Yield has been calculated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1966-67 to 1994-95 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Tamil Nadu:-&gt; Yield has been calculated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1966-67 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Andhra Pradesh:-&gt; Yield has been calculated for the years 1966-67 To 1969-70 and 1992-93 To 1995-96.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1970-71 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Meghalaya:-&gt; Yield has been calculated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1971-72 to 1975-76 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Manipur:-&gt; Yield has been calculated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1971-72 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Tripura:-&gt; Yield has been calculated for the years 1971-72 To 1979-80 and 1986-87 To 1995-96.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1973-74 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Dadra and Nagar Haveli:-&gt; Yield has been calculated for the years 1973-74 To 1979-80 and 1986-87 To 1995-96.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1975-76 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Arunachal Pradesh:-&gt; Yield has been calculated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1981-82 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Sikkim:-&gt; Yield has been calculated for the years 1981-82 To 1984-85, 1994-95 and 1995-96.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1990-91 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Nagaland:-&gt; Yield has been calculated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1992-93 to 1995-96 - Foodgrains: Cereals: Major Cereals: Wheat: Rabi/Total: Yield: Odisha:-&gt; Yield has been calculated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-17 to 2020-21 - Data for the years are Final Estimates as released on 25.05.2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-21 to 2020-21 - : All-India:-&gt; Data for the year 2020-21 are Final Estimates as released on 16.02.2022 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-22 to 2021-22 - : All-India:-&gt; Data for the year 2021-22 are 3rd Advance Estimates as released on 19.05.2022 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The yield rates given for all foodgrains have been worked out on the basis of production &amp; area figures taken in '000 units.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Descrption</t>
     </r>
@@ -383,7 +398,6 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -398,7 +412,7 @@
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -441,9 +455,26 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
@@ -521,7 +552,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -574,16 +605,44 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -591,14 +650,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -619,8 +674,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Y94"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15.4"/>
@@ -4753,441 +4808,755 @@
       <c r="J61" s="11"/>
       <c r="N61" s="11"/>
     </row>
-    <row r="69" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="13" t="s">
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="14" t="s">
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
+      <c r="Q62" s="13"/>
+      <c r="R62" s="13"/>
+      <c r="S62" s="13"/>
+      <c r="T62" s="13"/>
+      <c r="U62" s="13"/>
+      <c r="V62" s="13"/>
+      <c r="W62" s="13"/>
+      <c r="X62" s="13"/>
+      <c r="Y62" s="13"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B70" s="14"/>
-      <c r="C70" s="14"/>
-      <c r="D70" s="14"/>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
+      <c r="O63" s="14"/>
+      <c r="P63" s="14"/>
+      <c r="Q63" s="14"/>
+      <c r="R63" s="14"/>
+      <c r="S63" s="14"/>
+      <c r="T63" s="14"/>
+      <c r="U63" s="14"/>
+      <c r="V63" s="14"/>
+      <c r="W63" s="14"/>
+      <c r="X63" s="14"/>
+      <c r="Y63" s="14"/>
+    </row>
+    <row r="64" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="B64" s="14"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="14"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="14"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="14"/>
+      <c r="M64" s="14"/>
+      <c r="N64" s="14"/>
+      <c r="O64" s="14"/>
+      <c r="P64" s="14"/>
+      <c r="Q64" s="14"/>
+      <c r="R64" s="14"/>
+      <c r="S64" s="14"/>
+      <c r="T64" s="14"/>
+      <c r="U64" s="14"/>
+      <c r="V64" s="14"/>
+      <c r="W64" s="14"/>
+      <c r="X64" s="14"/>
+      <c r="Y64" s="14"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B65" s="15"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="15"/>
+      <c r="E65" s="15"/>
+      <c r="F65" s="15"/>
+      <c r="G65" s="15"/>
+      <c r="H65" s="15"/>
+      <c r="I65" s="15"/>
+      <c r="J65" s="15"/>
+      <c r="K65" s="15"/>
+      <c r="L65" s="15"/>
+      <c r="M65" s="15"/>
+      <c r="N65" s="15"/>
+      <c r="O65" s="15"/>
+      <c r="P65" s="15"/>
+      <c r="Q65" s="15"/>
+      <c r="R65" s="15"/>
+      <c r="S65" s="15"/>
+      <c r="T65" s="15"/>
+      <c r="U65" s="15"/>
+      <c r="V65" s="15"/>
+      <c r="W65" s="15"/>
+      <c r="X65" s="15"/>
+      <c r="Y65" s="15"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="B66" s="15"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="15"/>
+      <c r="E66" s="15"/>
+      <c r="F66" s="15"/>
+      <c r="G66" s="15"/>
+      <c r="H66" s="15"/>
+      <c r="I66" s="15"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="15"/>
+      <c r="L66" s="15"/>
+      <c r="M66" s="15"/>
+      <c r="N66" s="15"/>
+      <c r="O66" s="15"/>
+      <c r="P66" s="15"/>
+      <c r="Q66" s="15"/>
+      <c r="R66" s="15"/>
+      <c r="S66" s="15"/>
+      <c r="T66" s="15"/>
+      <c r="U66" s="15"/>
+      <c r="V66" s="15"/>
+      <c r="W66" s="15"/>
+      <c r="X66" s="15"/>
+      <c r="Y66" s="15"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" s="15"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="15"/>
+      <c r="E67" s="15"/>
+      <c r="F67" s="15"/>
+      <c r="G67" s="15"/>
+      <c r="H67" s="15"/>
+      <c r="I67" s="15"/>
+      <c r="J67" s="15"/>
+      <c r="K67" s="15"/>
+      <c r="L67" s="15"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="15"/>
+      <c r="O67" s="15"/>
+      <c r="P67" s="15"/>
+      <c r="Q67" s="15"/>
+      <c r="R67" s="15"/>
+      <c r="S67" s="15"/>
+      <c r="T67" s="15"/>
+      <c r="U67" s="15"/>
+      <c r="V67" s="15"/>
+      <c r="W67" s="15"/>
+      <c r="X67" s="15"/>
+      <c r="Y67" s="15"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B68" s="15"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="15"/>
+      <c r="E68" s="15"/>
+      <c r="F68" s="15"/>
+      <c r="G68" s="15"/>
+      <c r="H68" s="15"/>
+      <c r="I68" s="15"/>
+      <c r="J68" s="15"/>
+      <c r="K68" s="15"/>
+      <c r="L68" s="15"/>
+      <c r="M68" s="15"/>
+      <c r="N68" s="15"/>
+      <c r="O68" s="15"/>
+      <c r="P68" s="15"/>
+      <c r="Q68" s="15"/>
+      <c r="R68" s="15"/>
+      <c r="S68" s="15"/>
+      <c r="T68" s="15"/>
+      <c r="U68" s="15"/>
+      <c r="V68" s="15"/>
+      <c r="W68" s="15"/>
+      <c r="X68" s="15"/>
+      <c r="Y68" s="15"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="16"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="16"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
+      <c r="G69" s="16"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+      <c r="N69" s="16"/>
+      <c r="O69" s="16"/>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="16"/>
+      <c r="R69" s="16"/>
+      <c r="S69" s="16"/>
+      <c r="T69" s="16"/>
+      <c r="U69" s="16"/>
+      <c r="V69" s="16"/>
+      <c r="W69" s="16"/>
+      <c r="X69" s="16"/>
+      <c r="Y69" s="16"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="16"/>
+      <c r="I70" s="16"/>
+      <c r="J70" s="16"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
+      <c r="N70" s="16"/>
+      <c r="O70" s="16"/>
+      <c r="P70" s="16"/>
+      <c r="Q70" s="16"/>
+      <c r="R70" s="16"/>
+      <c r="S70" s="16"/>
+      <c r="T70" s="16"/>
+      <c r="U70" s="16"/>
+      <c r="V70" s="16"/>
+      <c r="W70" s="16"/>
+      <c r="X70" s="16"/>
+      <c r="Y70" s="16"/>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B71" s="15"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
-      <c r="H71" s="15"/>
-      <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
+      <c r="A71" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
+      <c r="L71" s="17"/>
+      <c r="M71" s="17"/>
+      <c r="N71" s="17"/>
+      <c r="O71" s="17"/>
+      <c r="P71" s="17"/>
+      <c r="Q71" s="17"/>
+      <c r="R71" s="17"/>
+      <c r="S71" s="17"/>
+      <c r="T71" s="17"/>
+      <c r="U71" s="17"/>
+      <c r="V71" s="17"/>
+      <c r="W71" s="17"/>
+      <c r="X71" s="17"/>
+      <c r="Y71" s="17"/>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16"/>
-      <c r="D72" s="16"/>
-      <c r="E72" s="16"/>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
-      <c r="H72" s="16"/>
-      <c r="I72" s="16"/>
-      <c r="J72" s="16"/>
-      <c r="K72" s="16"/>
-      <c r="L72" s="16"/>
-      <c r="M72" s="16"/>
+      <c r="A72" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="B72" s="18"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="18"/>
+      <c r="Q72" s="18"/>
+      <c r="R72" s="18"/>
+      <c r="S72" s="18"/>
+      <c r="T72" s="18"/>
+      <c r="U72" s="18"/>
+      <c r="V72" s="18"/>
+      <c r="W72" s="18"/>
+      <c r="X72" s="18"/>
+      <c r="Y72" s="18"/>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16"/>
-      <c r="D73" s="16"/>
-      <c r="E73" s="16"/>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="16"/>
-      <c r="I73" s="16"/>
-      <c r="J73" s="16"/>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+      <c r="A73" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
+      <c r="G73" s="19"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
+      <c r="J73" s="19"/>
+      <c r="K73" s="19"/>
+      <c r="L73" s="19"/>
+      <c r="M73" s="19"/>
+      <c r="N73" s="19"/>
+      <c r="O73" s="19"/>
+      <c r="P73" s="19"/>
+      <c r="Q73" s="19"/>
+      <c r="R73" s="19"/>
+      <c r="S73" s="19"/>
+      <c r="T73" s="19"/>
+      <c r="U73" s="19"/>
+      <c r="V73" s="19"/>
+      <c r="W73" s="19"/>
+      <c r="X73" s="19"/>
+      <c r="Y73" s="19"/>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="16"/>
-      <c r="E74" s="16"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="16"/>
-      <c r="H74" s="16"/>
-      <c r="I74" s="16"/>
-      <c r="J74" s="16"/>
-      <c r="K74" s="16"/>
-      <c r="L74" s="16"/>
-      <c r="M74" s="16"/>
+      <c r="A74" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="20"/>
+      <c r="L74" s="20"/>
+      <c r="M74" s="20"/>
+      <c r="N74" s="20"/>
+      <c r="O74" s="20"/>
+      <c r="P74" s="20"/>
+      <c r="Q74" s="20"/>
+      <c r="R74" s="20"/>
+      <c r="S74" s="20"/>
+      <c r="T74" s="20"/>
+      <c r="U74" s="20"/>
+      <c r="V74" s="20"/>
+      <c r="W74" s="20"/>
+      <c r="X74" s="20"/>
+      <c r="Y74" s="20"/>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
-      <c r="D75" s="16"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="16"/>
-      <c r="H75" s="16"/>
-      <c r="I75" s="16"/>
-      <c r="J75" s="16"/>
-      <c r="K75" s="16"/>
-      <c r="L75" s="16"/>
-      <c r="M75" s="16"/>
+      <c r="A75" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+      <c r="K75" s="20"/>
+      <c r="L75" s="20"/>
+      <c r="M75" s="20"/>
+      <c r="N75" s="20"/>
+      <c r="O75" s="20"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="20"/>
+      <c r="R75" s="20"/>
+      <c r="S75" s="20"/>
+      <c r="T75" s="20"/>
+      <c r="U75" s="20"/>
+      <c r="V75" s="20"/>
+      <c r="W75" s="20"/>
+      <c r="X75" s="20"/>
+      <c r="Y75" s="20"/>
     </row>
     <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
-      <c r="D76" s="17"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="17"/>
-      <c r="G76" s="17"/>
-      <c r="H76" s="17"/>
-      <c r="I76" s="17"/>
-      <c r="J76" s="17"/>
-      <c r="K76" s="17"/>
-      <c r="L76" s="17"/>
-      <c r="M76" s="17"/>
+      <c r="A76" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
+      <c r="K76" s="20"/>
+      <c r="L76" s="20"/>
+      <c r="M76" s="20"/>
+      <c r="N76" s="20"/>
+      <c r="O76" s="20"/>
+      <c r="P76" s="20"/>
+      <c r="Q76" s="20"/>
+      <c r="R76" s="20"/>
+      <c r="S76" s="20"/>
+      <c r="T76" s="20"/>
+      <c r="U76" s="20"/>
+      <c r="V76" s="20"/>
+      <c r="W76" s="20"/>
+      <c r="X76" s="20"/>
+      <c r="Y76" s="20"/>
     </row>
     <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
-      <c r="D77" s="16"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="16"/>
-      <c r="G77" s="16"/>
-      <c r="H77" s="16"/>
-      <c r="I77" s="16"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="16"/>
-      <c r="L77" s="16"/>
-      <c r="M77" s="16"/>
+      <c r="A77" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="20"/>
+      <c r="L77" s="20"/>
+      <c r="M77" s="20"/>
+      <c r="N77" s="20"/>
+      <c r="O77" s="20"/>
+      <c r="P77" s="20"/>
+      <c r="Q77" s="20"/>
+      <c r="R77" s="20"/>
+      <c r="S77" s="20"/>
+      <c r="T77" s="20"/>
+      <c r="U77" s="20"/>
+      <c r="V77" s="20"/>
+      <c r="W77" s="20"/>
+      <c r="X77" s="20"/>
+      <c r="Y77" s="20"/>
     </row>
     <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-      <c r="E78" s="16"/>
-      <c r="F78" s="16"/>
-      <c r="G78" s="16"/>
-      <c r="H78" s="16"/>
-      <c r="I78" s="16"/>
-      <c r="J78" s="16"/>
-      <c r="K78" s="16"/>
-      <c r="L78" s="16"/>
-      <c r="M78" s="16"/>
+      <c r="A78" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="21"/>
+      <c r="H78" s="21"/>
+      <c r="I78" s="21"/>
+      <c r="J78" s="21"/>
+      <c r="K78" s="21"/>
+      <c r="L78" s="21"/>
+      <c r="M78" s="21"/>
+      <c r="N78" s="21"/>
+      <c r="O78" s="21"/>
+      <c r="P78" s="21"/>
+      <c r="Q78" s="21"/>
+      <c r="R78" s="21"/>
+      <c r="S78" s="21"/>
+      <c r="T78" s="21"/>
+      <c r="U78" s="21"/>
+      <c r="V78" s="21"/>
+      <c r="W78" s="21"/>
+      <c r="X78" s="21"/>
+      <c r="Y78" s="21"/>
     </row>
     <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
-      <c r="H79" s="16"/>
-      <c r="I79" s="16"/>
-      <c r="J79" s="16"/>
-      <c r="K79" s="16"/>
-      <c r="L79" s="16"/>
-      <c r="M79" s="16"/>
+      <c r="A79" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="20"/>
+      <c r="J79" s="20"/>
+      <c r="K79" s="20"/>
+      <c r="L79" s="20"/>
+      <c r="M79" s="20"/>
+      <c r="N79" s="20"/>
+      <c r="O79" s="20"/>
+      <c r="P79" s="20"/>
+      <c r="Q79" s="20"/>
+      <c r="R79" s="20"/>
+      <c r="S79" s="20"/>
+      <c r="T79" s="20"/>
+      <c r="U79" s="20"/>
+      <c r="V79" s="20"/>
+      <c r="W79" s="20"/>
+      <c r="X79" s="20"/>
+      <c r="Y79" s="20"/>
     </row>
     <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
-      <c r="D80" s="16"/>
-      <c r="E80" s="16"/>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
-      <c r="H80" s="16"/>
-      <c r="I80" s="16"/>
-      <c r="J80" s="16"/>
-      <c r="K80" s="16"/>
-      <c r="L80" s="16"/>
-      <c r="M80" s="16"/>
+      <c r="A80" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="20"/>
+      <c r="J80" s="20"/>
+      <c r="K80" s="20"/>
+      <c r="L80" s="20"/>
+      <c r="M80" s="20"/>
+      <c r="N80" s="20"/>
+      <c r="O80" s="20"/>
+      <c r="P80" s="20"/>
+      <c r="Q80" s="20"/>
+      <c r="R80" s="20"/>
+      <c r="S80" s="20"/>
+      <c r="T80" s="20"/>
+      <c r="U80" s="20"/>
+      <c r="V80" s="20"/>
+      <c r="W80" s="20"/>
+      <c r="X80" s="20"/>
+      <c r="Y80" s="20"/>
     </row>
     <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16"/>
-      <c r="H81" s="16"/>
-      <c r="I81" s="16"/>
-      <c r="J81" s="16"/>
-      <c r="K81" s="16"/>
-      <c r="L81" s="16"/>
-      <c r="M81" s="16"/>
+      <c r="A81" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
+      <c r="K81" s="20"/>
+      <c r="L81" s="20"/>
+      <c r="M81" s="20"/>
+      <c r="N81" s="20"/>
+      <c r="O81" s="20"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+      <c r="S81" s="20"/>
+      <c r="T81" s="20"/>
+      <c r="U81" s="20"/>
+      <c r="V81" s="20"/>
+      <c r="W81" s="20"/>
+      <c r="X81" s="20"/>
+      <c r="Y81" s="20"/>
     </row>
     <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B82" s="16"/>
-      <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
-      <c r="H82" s="16"/>
-      <c r="I82" s="16"/>
-      <c r="J82" s="16"/>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
+      <c r="A82" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
+      <c r="J82" s="20"/>
+      <c r="K82" s="20"/>
+      <c r="L82" s="20"/>
+      <c r="M82" s="20"/>
+      <c r="N82" s="20"/>
+      <c r="O82" s="20"/>
+      <c r="P82" s="20"/>
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="20"/>
+      <c r="U82" s="20"/>
+      <c r="V82" s="20"/>
+      <c r="W82" s="20"/>
+      <c r="X82" s="20"/>
+      <c r="Y82" s="20"/>
     </row>
     <row r="83" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
-      <c r="G83" s="16"/>
-      <c r="H83" s="16"/>
-      <c r="I83" s="16"/>
-      <c r="J83" s="16"/>
-      <c r="K83" s="16"/>
-      <c r="L83" s="16"/>
-      <c r="M83" s="16"/>
+      <c r="A83" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="20"/>
+      <c r="G83" s="20"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="20"/>
+      <c r="J83" s="20"/>
+      <c r="K83" s="20"/>
+      <c r="L83" s="20"/>
+      <c r="M83" s="20"/>
+      <c r="N83" s="20"/>
+      <c r="O83" s="20"/>
+      <c r="P83" s="20"/>
+      <c r="Q83" s="20"/>
+      <c r="R83" s="20"/>
+      <c r="S83" s="20"/>
+      <c r="T83" s="20"/>
+      <c r="U83" s="20"/>
+      <c r="V83" s="20"/>
+      <c r="W83" s="20"/>
+      <c r="X83" s="20"/>
+      <c r="Y83" s="20"/>
     </row>
     <row r="84" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
-      <c r="G84" s="16"/>
-      <c r="H84" s="16"/>
-      <c r="I84" s="16"/>
-      <c r="J84" s="16"/>
-      <c r="K84" s="16"/>
-      <c r="L84" s="16"/>
-      <c r="M84" s="16"/>
+      <c r="A84" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B84" s="20"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="20"/>
+      <c r="K84" s="20"/>
+      <c r="L84" s="20"/>
+      <c r="M84" s="20"/>
+      <c r="N84" s="20"/>
+      <c r="O84" s="20"/>
+      <c r="P84" s="20"/>
+      <c r="Q84" s="20"/>
+      <c r="R84" s="20"/>
+      <c r="S84" s="20"/>
+      <c r="T84" s="20"/>
+      <c r="U84" s="20"/>
+      <c r="V84" s="20"/>
+      <c r="W84" s="20"/>
+      <c r="X84" s="20"/>
+      <c r="Y84" s="20"/>
     </row>
     <row r="85" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16"/>
-      <c r="E85" s="16"/>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
-      <c r="H85" s="16"/>
-      <c r="I85" s="16"/>
-      <c r="J85" s="16"/>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
+      <c r="A85" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B85" s="22"/>
+      <c r="C85" s="22"/>
+      <c r="D85" s="22"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="22"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="22"/>
+      <c r="J85" s="22"/>
+      <c r="K85" s="22"/>
+      <c r="L85" s="22"/>
+      <c r="M85" s="22"/>
+      <c r="N85" s="22"/>
+      <c r="O85" s="22"/>
+      <c r="P85" s="22"/>
+      <c r="Q85" s="22"/>
+      <c r="R85" s="22"/>
+      <c r="S85" s="22"/>
+      <c r="T85" s="22"/>
+      <c r="U85" s="22"/>
+      <c r="V85" s="22"/>
+      <c r="W85" s="22"/>
+      <c r="X85" s="22"/>
+      <c r="Y85" s="22"/>
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16"/>
-      <c r="E86" s="16"/>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-      <c r="H86" s="16"/>
-      <c r="I86" s="16"/>
-      <c r="J86" s="16"/>
-      <c r="K86" s="16"/>
-      <c r="L86" s="16"/>
-      <c r="M86" s="16"/>
+      <c r="M86" s="23"/>
     </row>
     <row r="87" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
-      <c r="D87" s="16"/>
-      <c r="E87" s="16"/>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
-      <c r="H87" s="16"/>
-      <c r="I87" s="16"/>
-      <c r="J87" s="16"/>
-      <c r="K87" s="16"/>
-      <c r="L87" s="16"/>
-      <c r="M87" s="16"/>
+      <c r="M87" s="23"/>
     </row>
     <row r="88" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="B88" s="18"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="18"/>
-      <c r="I88" s="18"/>
-      <c r="J88" s="18"/>
-      <c r="K88" s="18"/>
-      <c r="L88" s="18"/>
-      <c r="M88" s="18"/>
+      <c r="M88" s="23"/>
     </row>
     <row r="89" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16"/>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16"/>
-      <c r="G89" s="16"/>
-      <c r="H89" s="16"/>
-      <c r="I89" s="16"/>
-      <c r="J89" s="16"/>
-      <c r="K89" s="16"/>
-      <c r="L89" s="16"/>
-      <c r="M89" s="16"/>
+      <c r="M89" s="23"/>
     </row>
     <row r="90" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B90" s="16"/>
-      <c r="C90" s="16"/>
-      <c r="D90" s="16"/>
-      <c r="E90" s="16"/>
-      <c r="F90" s="16"/>
-      <c r="G90" s="16"/>
-      <c r="H90" s="16"/>
-      <c r="I90" s="16"/>
-      <c r="J90" s="16"/>
-      <c r="K90" s="16"/>
-      <c r="L90" s="16"/>
-      <c r="M90" s="16"/>
+      <c r="M90" s="24"/>
     </row>
     <row r="91" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="16"/>
-      <c r="G91" s="16"/>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16"/>
-      <c r="J91" s="16"/>
-      <c r="K91" s="16"/>
-      <c r="L91" s="16"/>
-      <c r="M91" s="16"/>
+      <c r="M91" s="23"/>
     </row>
     <row r="92" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
-      <c r="G92" s="19"/>
-      <c r="H92" s="19"/>
-      <c r="I92" s="19"/>
-      <c r="J92" s="19"/>
-      <c r="K92" s="19"/>
-      <c r="L92" s="19"/>
-      <c r="M92" s="19"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="M92" s="23"/>
+    </row>
+    <row r="93" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M93" s="23"/>
+    </row>
+    <row r="94" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="M94" s="25"/>
+    </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A69:M69"/>
-    <mergeCell ref="A70:M70"/>
-    <mergeCell ref="A71:M71"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A73:M73"/>
-    <mergeCell ref="A74:M74"/>
-    <mergeCell ref="A75:M75"/>
-    <mergeCell ref="A76:M76"/>
-    <mergeCell ref="A77:M77"/>
-    <mergeCell ref="A78:M78"/>
-    <mergeCell ref="A79:M79"/>
-    <mergeCell ref="A80:M80"/>
-    <mergeCell ref="A81:M81"/>
-    <mergeCell ref="A82:M82"/>
-    <mergeCell ref="A83:M83"/>
-    <mergeCell ref="A84:M84"/>
-    <mergeCell ref="A85:M85"/>
-    <mergeCell ref="A86:M86"/>
-    <mergeCell ref="A87:M87"/>
-    <mergeCell ref="A88:M88"/>
-    <mergeCell ref="A89:M89"/>
-    <mergeCell ref="A90:M90"/>
-    <mergeCell ref="A91:M91"/>
-    <mergeCell ref="A92:M92"/>
+    <mergeCell ref="A62:Y62"/>
+    <mergeCell ref="A63:Y63"/>
+    <mergeCell ref="A64:Y64"/>
+    <mergeCell ref="A65:Y65"/>
+    <mergeCell ref="A66:Y66"/>
+    <mergeCell ref="A67:Y67"/>
+    <mergeCell ref="A68:Y68"/>
+    <mergeCell ref="A69:Y69"/>
+    <mergeCell ref="A70:Y70"/>
+    <mergeCell ref="A71:Y71"/>
+    <mergeCell ref="A72:Y72"/>
+    <mergeCell ref="A73:Y73"/>
+    <mergeCell ref="A74:Y74"/>
+    <mergeCell ref="A75:Y75"/>
+    <mergeCell ref="A76:Y76"/>
+    <mergeCell ref="A77:Y77"/>
+    <mergeCell ref="A78:Y78"/>
+    <mergeCell ref="A79:Y79"/>
+    <mergeCell ref="A80:Y80"/>
+    <mergeCell ref="A81:Y81"/>
+    <mergeCell ref="A82:Y82"/>
+    <mergeCell ref="A83:Y83"/>
+    <mergeCell ref="A84:Y84"/>
+    <mergeCell ref="A85:Y85"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 7.xlsx
+++ b/agriculture 7.xlsx
@@ -277,7 +277,7 @@
     <t xml:space="preserve">2021-22</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <r>
@@ -287,6 +287,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source:</t>
     </r>
@@ -296,6 +297,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> EPWRF (Economic &amp; Political Weekly Research Foundation) (1950-2021)</t>
     </r>
@@ -308,6 +310,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Note:- </t>
     </r>
@@ -317,6 +320,7 @@
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Arunachal Pradesh:-&gt; Data for Arunachal Pradesh referred as North-East Frontier Agency (NEFA) for the years 1962-63 To 1969-70.</t>
     </r>
@@ -389,6 +393,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Descrption</t>
     </r>
@@ -398,6 +403,7 @@
         <color rgb="FF000000"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">: Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -412,7 +418,7 @@
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -455,29 +461,19 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -552,7 +548,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -605,19 +601,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -629,15 +621,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -646,14 +638,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -675,7 +663,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Y94"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="2" style="0" width="15.4"/>
@@ -4896,640 +4884,640 @@
       <c r="Y64" s="14"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15"/>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
-      <c r="M65" s="15"/>
-      <c r="N65" s="15"/>
-      <c r="O65" s="15"/>
-      <c r="P65" s="15"/>
-      <c r="Q65" s="15"/>
-      <c r="R65" s="15"/>
-      <c r="S65" s="15"/>
-      <c r="T65" s="15"/>
-      <c r="U65" s="15"/>
-      <c r="V65" s="15"/>
-      <c r="W65" s="15"/>
-      <c r="X65" s="15"/>
-      <c r="Y65" s="15"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+      <c r="K65" s="13"/>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13"/>
+      <c r="O65" s="13"/>
+      <c r="P65" s="13"/>
+      <c r="Q65" s="13"/>
+      <c r="R65" s="13"/>
+      <c r="S65" s="13"/>
+      <c r="T65" s="13"/>
+      <c r="U65" s="13"/>
+      <c r="V65" s="13"/>
+      <c r="W65" s="13"/>
+      <c r="X65" s="13"/>
+      <c r="Y65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="15" t="s">
+      <c r="A66" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="15"/>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
-      <c r="M66" s="15"/>
-      <c r="N66" s="15"/>
-      <c r="O66" s="15"/>
-      <c r="P66" s="15"/>
-      <c r="Q66" s="15"/>
-      <c r="R66" s="15"/>
-      <c r="S66" s="15"/>
-      <c r="T66" s="15"/>
-      <c r="U66" s="15"/>
-      <c r="V66" s="15"/>
-      <c r="W66" s="15"/>
-      <c r="X66" s="15"/>
-      <c r="Y66" s="15"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="D66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13"/>
+      <c r="O66" s="13"/>
+      <c r="P66" s="13"/>
+      <c r="Q66" s="13"/>
+      <c r="R66" s="13"/>
+      <c r="S66" s="13"/>
+      <c r="T66" s="13"/>
+      <c r="U66" s="13"/>
+      <c r="V66" s="13"/>
+      <c r="W66" s="13"/>
+      <c r="X66" s="13"/>
+      <c r="Y66" s="13"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15" t="s">
+      <c r="A67" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="15"/>
-      <c r="R67" s="15"/>
-      <c r="S67" s="15"/>
-      <c r="T67" s="15"/>
-      <c r="U67" s="15"/>
-      <c r="V67" s="15"/>
-      <c r="W67" s="15"/>
-      <c r="X67" s="15"/>
-      <c r="Y67" s="15"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13"/>
+      <c r="O67" s="13"/>
+      <c r="P67" s="13"/>
+      <c r="Q67" s="13"/>
+      <c r="R67" s="13"/>
+      <c r="S67" s="13"/>
+      <c r="T67" s="13"/>
+      <c r="U67" s="13"/>
+      <c r="V67" s="13"/>
+      <c r="W67" s="13"/>
+      <c r="X67" s="13"/>
+      <c r="Y67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="15" t="s">
+      <c r="A68" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
-      <c r="H68" s="15"/>
-      <c r="I68" s="15"/>
-      <c r="J68" s="15"/>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
-      <c r="M68" s="15"/>
-      <c r="N68" s="15"/>
-      <c r="O68" s="15"/>
-      <c r="P68" s="15"/>
-      <c r="Q68" s="15"/>
-      <c r="R68" s="15"/>
-      <c r="S68" s="15"/>
-      <c r="T68" s="15"/>
-      <c r="U68" s="15"/>
-      <c r="V68" s="15"/>
-      <c r="W68" s="15"/>
-      <c r="X68" s="15"/>
-      <c r="Y68" s="15"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13"/>
+      <c r="O68" s="13"/>
+      <c r="P68" s="13"/>
+      <c r="Q68" s="13"/>
+      <c r="R68" s="13"/>
+      <c r="S68" s="13"/>
+      <c r="T68" s="13"/>
+      <c r="U68" s="13"/>
+      <c r="V68" s="13"/>
+      <c r="W68" s="13"/>
+      <c r="X68" s="13"/>
+      <c r="Y68" s="13"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
-      <c r="D69" s="16"/>
-      <c r="E69" s="16"/>
-      <c r="F69" s="16"/>
-      <c r="G69" s="16"/>
-      <c r="H69" s="16"/>
-      <c r="I69" s="16"/>
-      <c r="J69" s="16"/>
-      <c r="K69" s="16"/>
-      <c r="L69" s="16"/>
-      <c r="M69" s="16"/>
-      <c r="N69" s="16"/>
-      <c r="O69" s="16"/>
-      <c r="P69" s="16"/>
-      <c r="Q69" s="16"/>
-      <c r="R69" s="16"/>
-      <c r="S69" s="16"/>
-      <c r="T69" s="16"/>
-      <c r="U69" s="16"/>
-      <c r="V69" s="16"/>
-      <c r="W69" s="16"/>
-      <c r="X69" s="16"/>
-      <c r="Y69" s="16"/>
+      <c r="B69" s="15"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="15"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="15"/>
+      <c r="G69" s="15"/>
+      <c r="H69" s="15"/>
+      <c r="I69" s="15"/>
+      <c r="J69" s="15"/>
+      <c r="K69" s="15"/>
+      <c r="L69" s="15"/>
+      <c r="M69" s="15"/>
+      <c r="N69" s="15"/>
+      <c r="O69" s="15"/>
+      <c r="P69" s="15"/>
+      <c r="Q69" s="15"/>
+      <c r="R69" s="15"/>
+      <c r="S69" s="15"/>
+      <c r="T69" s="15"/>
+      <c r="U69" s="15"/>
+      <c r="V69" s="15"/>
+      <c r="W69" s="15"/>
+      <c r="X69" s="15"/>
+      <c r="Y69" s="15"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
-      <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="16"/>
-      <c r="I70" s="16"/>
-      <c r="J70" s="16"/>
-      <c r="K70" s="16"/>
-      <c r="L70" s="16"/>
-      <c r="M70" s="16"/>
-      <c r="N70" s="16"/>
-      <c r="O70" s="16"/>
-      <c r="P70" s="16"/>
-      <c r="Q70" s="16"/>
-      <c r="R70" s="16"/>
-      <c r="S70" s="16"/>
-      <c r="T70" s="16"/>
-      <c r="U70" s="16"/>
-      <c r="V70" s="16"/>
-      <c r="W70" s="16"/>
-      <c r="X70" s="16"/>
-      <c r="Y70" s="16"/>
+      <c r="B70" s="15"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="15"/>
+      <c r="E70" s="15"/>
+      <c r="F70" s="15"/>
+      <c r="G70" s="15"/>
+      <c r="H70" s="15"/>
+      <c r="I70" s="15"/>
+      <c r="J70" s="15"/>
+      <c r="K70" s="15"/>
+      <c r="L70" s="15"/>
+      <c r="M70" s="15"/>
+      <c r="N70" s="15"/>
+      <c r="O70" s="15"/>
+      <c r="P70" s="15"/>
+      <c r="Q70" s="15"/>
+      <c r="R70" s="15"/>
+      <c r="S70" s="15"/>
+      <c r="T70" s="15"/>
+      <c r="U70" s="15"/>
+      <c r="V70" s="15"/>
+      <c r="W70" s="15"/>
+      <c r="X70" s="15"/>
+      <c r="Y70" s="15"/>
     </row>
     <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="17" t="s">
+      <c r="A71" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
-      <c r="N71" s="17"/>
-      <c r="O71" s="17"/>
-      <c r="P71" s="17"/>
-      <c r="Q71" s="17"/>
-      <c r="R71" s="17"/>
-      <c r="S71" s="17"/>
-      <c r="T71" s="17"/>
-      <c r="U71" s="17"/>
-      <c r="V71" s="17"/>
-      <c r="W71" s="17"/>
-      <c r="X71" s="17"/>
-      <c r="Y71" s="17"/>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
+      <c r="G71" s="16"/>
+      <c r="H71" s="16"/>
+      <c r="I71" s="16"/>
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
+      <c r="N71" s="16"/>
+      <c r="O71" s="16"/>
+      <c r="P71" s="16"/>
+      <c r="Q71" s="16"/>
+      <c r="R71" s="16"/>
+      <c r="S71" s="16"/>
+      <c r="T71" s="16"/>
+      <c r="U71" s="16"/>
+      <c r="V71" s="16"/>
+      <c r="W71" s="16"/>
+      <c r="X71" s="16"/>
+      <c r="Y71" s="16"/>
     </row>
     <row r="72" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="18" t="s">
+      <c r="A72" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B72" s="18"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="18"/>
-      <c r="H72" s="18"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="18"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
-      <c r="N72" s="18"/>
-      <c r="O72" s="18"/>
-      <c r="P72" s="18"/>
-      <c r="Q72" s="18"/>
-      <c r="R72" s="18"/>
-      <c r="S72" s="18"/>
-      <c r="T72" s="18"/>
-      <c r="U72" s="18"/>
-      <c r="V72" s="18"/>
-      <c r="W72" s="18"/>
-      <c r="X72" s="18"/>
-      <c r="Y72" s="18"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
+      <c r="L72" s="17"/>
+      <c r="M72" s="17"/>
+      <c r="N72" s="17"/>
+      <c r="O72" s="17"/>
+      <c r="P72" s="17"/>
+      <c r="Q72" s="17"/>
+      <c r="R72" s="17"/>
+      <c r="S72" s="17"/>
+      <c r="T72" s="17"/>
+      <c r="U72" s="17"/>
+      <c r="V72" s="17"/>
+      <c r="W72" s="17"/>
+      <c r="X72" s="17"/>
+      <c r="Y72" s="17"/>
     </row>
     <row r="73" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="19" t="s">
+      <c r="A73" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="19"/>
-      <c r="J73" s="19"/>
-      <c r="K73" s="19"/>
-      <c r="L73" s="19"/>
-      <c r="M73" s="19"/>
-      <c r="N73" s="19"/>
-      <c r="O73" s="19"/>
-      <c r="P73" s="19"/>
-      <c r="Q73" s="19"/>
-      <c r="R73" s="19"/>
-      <c r="S73" s="19"/>
-      <c r="T73" s="19"/>
-      <c r="U73" s="19"/>
-      <c r="V73" s="19"/>
-      <c r="W73" s="19"/>
-      <c r="X73" s="19"/>
-      <c r="Y73" s="19"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="18"/>
+      <c r="Q73" s="18"/>
+      <c r="R73" s="18"/>
+      <c r="S73" s="18"/>
+      <c r="T73" s="18"/>
+      <c r="U73" s="18"/>
+      <c r="V73" s="18"/>
+      <c r="W73" s="18"/>
+      <c r="X73" s="18"/>
+      <c r="Y73" s="18"/>
     </row>
     <row r="74" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="20"/>
-      <c r="K74" s="20"/>
-      <c r="L74" s="20"/>
-      <c r="M74" s="20"/>
-      <c r="N74" s="20"/>
-      <c r="O74" s="20"/>
-      <c r="P74" s="20"/>
-      <c r="Q74" s="20"/>
-      <c r="R74" s="20"/>
-      <c r="S74" s="20"/>
-      <c r="T74" s="20"/>
-      <c r="U74" s="20"/>
-      <c r="V74" s="20"/>
-      <c r="W74" s="20"/>
-      <c r="X74" s="20"/>
-      <c r="Y74" s="20"/>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="19"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="19"/>
+      <c r="M74" s="19"/>
+      <c r="N74" s="19"/>
+      <c r="O74" s="19"/>
+      <c r="P74" s="19"/>
+      <c r="Q74" s="19"/>
+      <c r="R74" s="19"/>
+      <c r="S74" s="19"/>
+      <c r="T74" s="19"/>
+      <c r="U74" s="19"/>
+      <c r="V74" s="19"/>
+      <c r="W74" s="19"/>
+      <c r="X74" s="19"/>
+      <c r="Y74" s="19"/>
     </row>
     <row r="75" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="20" t="s">
+      <c r="A75" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
-      <c r="H75" s="20"/>
-      <c r="I75" s="20"/>
-      <c r="J75" s="20"/>
-      <c r="K75" s="20"/>
-      <c r="L75" s="20"/>
-      <c r="M75" s="20"/>
-      <c r="N75" s="20"/>
-      <c r="O75" s="20"/>
-      <c r="P75" s="20"/>
-      <c r="Q75" s="20"/>
-      <c r="R75" s="20"/>
-      <c r="S75" s="20"/>
-      <c r="T75" s="20"/>
-      <c r="U75" s="20"/>
-      <c r="V75" s="20"/>
-      <c r="W75" s="20"/>
-      <c r="X75" s="20"/>
-      <c r="Y75" s="20"/>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="19"/>
+      <c r="F75" s="19"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19"/>
+      <c r="K75" s="19"/>
+      <c r="L75" s="19"/>
+      <c r="M75" s="19"/>
+      <c r="N75" s="19"/>
+      <c r="O75" s="19"/>
+      <c r="P75" s="19"/>
+      <c r="Q75" s="19"/>
+      <c r="R75" s="19"/>
+      <c r="S75" s="19"/>
+      <c r="T75" s="19"/>
+      <c r="U75" s="19"/>
+      <c r="V75" s="19"/>
+      <c r="W75" s="19"/>
+      <c r="X75" s="19"/>
+      <c r="Y75" s="19"/>
     </row>
     <row r="76" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="20" t="s">
+      <c r="A76" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
-      <c r="H76" s="20"/>
-      <c r="I76" s="20"/>
-      <c r="J76" s="20"/>
-      <c r="K76" s="20"/>
-      <c r="L76" s="20"/>
-      <c r="M76" s="20"/>
-      <c r="N76" s="20"/>
-      <c r="O76" s="20"/>
-      <c r="P76" s="20"/>
-      <c r="Q76" s="20"/>
-      <c r="R76" s="20"/>
-      <c r="S76" s="20"/>
-      <c r="T76" s="20"/>
-      <c r="U76" s="20"/>
-      <c r="V76" s="20"/>
-      <c r="W76" s="20"/>
-      <c r="X76" s="20"/>
-      <c r="Y76" s="20"/>
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
+      <c r="L76" s="19"/>
+      <c r="M76" s="19"/>
+      <c r="N76" s="19"/>
+      <c r="O76" s="19"/>
+      <c r="P76" s="19"/>
+      <c r="Q76" s="19"/>
+      <c r="R76" s="19"/>
+      <c r="S76" s="19"/>
+      <c r="T76" s="19"/>
+      <c r="U76" s="19"/>
+      <c r="V76" s="19"/>
+      <c r="W76" s="19"/>
+      <c r="X76" s="19"/>
+      <c r="Y76" s="19"/>
     </row>
     <row r="77" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="20" t="s">
+      <c r="A77" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
-      <c r="D77" s="20"/>
-      <c r="E77" s="20"/>
-      <c r="F77" s="20"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="20"/>
-      <c r="I77" s="20"/>
-      <c r="J77" s="20"/>
-      <c r="K77" s="20"/>
-      <c r="L77" s="20"/>
-      <c r="M77" s="20"/>
-      <c r="N77" s="20"/>
-      <c r="O77" s="20"/>
-      <c r="P77" s="20"/>
-      <c r="Q77" s="20"/>
-      <c r="R77" s="20"/>
-      <c r="S77" s="20"/>
-      <c r="T77" s="20"/>
-      <c r="U77" s="20"/>
-      <c r="V77" s="20"/>
-      <c r="W77" s="20"/>
-      <c r="X77" s="20"/>
-      <c r="Y77" s="20"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19"/>
+      <c r="K77" s="19"/>
+      <c r="L77" s="19"/>
+      <c r="M77" s="19"/>
+      <c r="N77" s="19"/>
+      <c r="O77" s="19"/>
+      <c r="P77" s="19"/>
+      <c r="Q77" s="19"/>
+      <c r="R77" s="19"/>
+      <c r="S77" s="19"/>
+      <c r="T77" s="19"/>
+      <c r="U77" s="19"/>
+      <c r="V77" s="19"/>
+      <c r="W77" s="19"/>
+      <c r="X77" s="19"/>
+      <c r="Y77" s="19"/>
     </row>
     <row r="78" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="21" t="s">
+      <c r="A78" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B78" s="21"/>
-      <c r="C78" s="21"/>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
-      <c r="L78" s="21"/>
-      <c r="M78" s="21"/>
-      <c r="N78" s="21"/>
-      <c r="O78" s="21"/>
-      <c r="P78" s="21"/>
-      <c r="Q78" s="21"/>
-      <c r="R78" s="21"/>
-      <c r="S78" s="21"/>
-      <c r="T78" s="21"/>
-      <c r="U78" s="21"/>
-      <c r="V78" s="21"/>
-      <c r="W78" s="21"/>
-      <c r="X78" s="21"/>
-      <c r="Y78" s="21"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
+      <c r="J78" s="20"/>
+      <c r="K78" s="20"/>
+      <c r="L78" s="20"/>
+      <c r="M78" s="20"/>
+      <c r="N78" s="20"/>
+      <c r="O78" s="20"/>
+      <c r="P78" s="20"/>
+      <c r="Q78" s="20"/>
+      <c r="R78" s="20"/>
+      <c r="S78" s="20"/>
+      <c r="T78" s="20"/>
+      <c r="U78" s="20"/>
+      <c r="V78" s="20"/>
+      <c r="W78" s="20"/>
+      <c r="X78" s="20"/>
+      <c r="Y78" s="20"/>
     </row>
     <row r="79" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="20" t="s">
+      <c r="A79" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20"/>
-      <c r="E79" s="20"/>
-      <c r="F79" s="20"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="20"/>
-      <c r="I79" s="20"/>
-      <c r="J79" s="20"/>
-      <c r="K79" s="20"/>
-      <c r="L79" s="20"/>
-      <c r="M79" s="20"/>
-      <c r="N79" s="20"/>
-      <c r="O79" s="20"/>
-      <c r="P79" s="20"/>
-      <c r="Q79" s="20"/>
-      <c r="R79" s="20"/>
-      <c r="S79" s="20"/>
-      <c r="T79" s="20"/>
-      <c r="U79" s="20"/>
-      <c r="V79" s="20"/>
-      <c r="W79" s="20"/>
-      <c r="X79" s="20"/>
-      <c r="Y79" s="20"/>
+      <c r="B79" s="19"/>
+      <c r="C79" s="19"/>
+      <c r="D79" s="19"/>
+      <c r="E79" s="19"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="19"/>
+      <c r="I79" s="19"/>
+      <c r="J79" s="19"/>
+      <c r="K79" s="19"/>
+      <c r="L79" s="19"/>
+      <c r="M79" s="19"/>
+      <c r="N79" s="19"/>
+      <c r="O79" s="19"/>
+      <c r="P79" s="19"/>
+      <c r="Q79" s="19"/>
+      <c r="R79" s="19"/>
+      <c r="S79" s="19"/>
+      <c r="T79" s="19"/>
+      <c r="U79" s="19"/>
+      <c r="V79" s="19"/>
+      <c r="W79" s="19"/>
+      <c r="X79" s="19"/>
+      <c r="Y79" s="19"/>
     </row>
     <row r="80" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="20" t="s">
+      <c r="A80" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="B80" s="20"/>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20"/>
-      <c r="E80" s="20"/>
-      <c r="F80" s="20"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="20"/>
-      <c r="I80" s="20"/>
-      <c r="J80" s="20"/>
-      <c r="K80" s="20"/>
-      <c r="L80" s="20"/>
-      <c r="M80" s="20"/>
-      <c r="N80" s="20"/>
-      <c r="O80" s="20"/>
-      <c r="P80" s="20"/>
-      <c r="Q80" s="20"/>
-      <c r="R80" s="20"/>
-      <c r="S80" s="20"/>
-      <c r="T80" s="20"/>
-      <c r="U80" s="20"/>
-      <c r="V80" s="20"/>
-      <c r="W80" s="20"/>
-      <c r="X80" s="20"/>
-      <c r="Y80" s="20"/>
+      <c r="B80" s="19"/>
+      <c r="C80" s="19"/>
+      <c r="D80" s="19"/>
+      <c r="E80" s="19"/>
+      <c r="F80" s="19"/>
+      <c r="G80" s="19"/>
+      <c r="H80" s="19"/>
+      <c r="I80" s="19"/>
+      <c r="J80" s="19"/>
+      <c r="K80" s="19"/>
+      <c r="L80" s="19"/>
+      <c r="M80" s="19"/>
+      <c r="N80" s="19"/>
+      <c r="O80" s="19"/>
+      <c r="P80" s="19"/>
+      <c r="Q80" s="19"/>
+      <c r="R80" s="19"/>
+      <c r="S80" s="19"/>
+      <c r="T80" s="19"/>
+      <c r="U80" s="19"/>
+      <c r="V80" s="19"/>
+      <c r="W80" s="19"/>
+      <c r="X80" s="19"/>
+      <c r="Y80" s="19"/>
     </row>
     <row r="81" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="B81" s="20"/>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20"/>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-      <c r="J81" s="20"/>
-      <c r="K81" s="20"/>
-      <c r="L81" s="20"/>
-      <c r="M81" s="20"/>
-      <c r="N81" s="20"/>
-      <c r="O81" s="20"/>
-      <c r="P81" s="20"/>
-      <c r="Q81" s="20"/>
-      <c r="R81" s="20"/>
-      <c r="S81" s="20"/>
-      <c r="T81" s="20"/>
-      <c r="U81" s="20"/>
-      <c r="V81" s="20"/>
-      <c r="W81" s="20"/>
-      <c r="X81" s="20"/>
-      <c r="Y81" s="20"/>
+      <c r="B81" s="19"/>
+      <c r="C81" s="19"/>
+      <c r="D81" s="19"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="19"/>
+      <c r="I81" s="19"/>
+      <c r="J81" s="19"/>
+      <c r="K81" s="19"/>
+      <c r="L81" s="19"/>
+      <c r="M81" s="19"/>
+      <c r="N81" s="19"/>
+      <c r="O81" s="19"/>
+      <c r="P81" s="19"/>
+      <c r="Q81" s="19"/>
+      <c r="R81" s="19"/>
+      <c r="S81" s="19"/>
+      <c r="T81" s="19"/>
+      <c r="U81" s="19"/>
+      <c r="V81" s="19"/>
+      <c r="W81" s="19"/>
+      <c r="X81" s="19"/>
+      <c r="Y81" s="19"/>
     </row>
     <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20"/>
-      <c r="H82" s="20"/>
-      <c r="I82" s="20"/>
-      <c r="J82" s="20"/>
-      <c r="K82" s="20"/>
-      <c r="L82" s="20"/>
-      <c r="M82" s="20"/>
-      <c r="N82" s="20"/>
-      <c r="O82" s="20"/>
-      <c r="P82" s="20"/>
-      <c r="Q82" s="20"/>
-      <c r="R82" s="20"/>
-      <c r="S82" s="20"/>
-      <c r="T82" s="20"/>
-      <c r="U82" s="20"/>
-      <c r="V82" s="20"/>
-      <c r="W82" s="20"/>
-      <c r="X82" s="20"/>
-      <c r="Y82" s="20"/>
+      <c r="B82" s="19"/>
+      <c r="C82" s="19"/>
+      <c r="D82" s="19"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="19"/>
+      <c r="L82" s="19"/>
+      <c r="M82" s="19"/>
+      <c r="N82" s="19"/>
+      <c r="O82" s="19"/>
+      <c r="P82" s="19"/>
+      <c r="Q82" s="19"/>
+      <c r="R82" s="19"/>
+      <c r="S82" s="19"/>
+      <c r="T82" s="19"/>
+      <c r="U82" s="19"/>
+      <c r="V82" s="19"/>
+      <c r="W82" s="19"/>
+      <c r="X82" s="19"/>
+      <c r="Y82" s="19"/>
     </row>
     <row r="83" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="20" t="s">
+      <c r="A83" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="B83" s="20"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
-      <c r="J83" s="20"/>
-      <c r="K83" s="20"/>
-      <c r="L83" s="20"/>
-      <c r="M83" s="20"/>
-      <c r="N83" s="20"/>
-      <c r="O83" s="20"/>
-      <c r="P83" s="20"/>
-      <c r="Q83" s="20"/>
-      <c r="R83" s="20"/>
-      <c r="S83" s="20"/>
-      <c r="T83" s="20"/>
-      <c r="U83" s="20"/>
-      <c r="V83" s="20"/>
-      <c r="W83" s="20"/>
-      <c r="X83" s="20"/>
-      <c r="Y83" s="20"/>
+      <c r="B83" s="19"/>
+      <c r="C83" s="19"/>
+      <c r="D83" s="19"/>
+      <c r="E83" s="19"/>
+      <c r="F83" s="19"/>
+      <c r="G83" s="19"/>
+      <c r="H83" s="19"/>
+      <c r="I83" s="19"/>
+      <c r="J83" s="19"/>
+      <c r="K83" s="19"/>
+      <c r="L83" s="19"/>
+      <c r="M83" s="19"/>
+      <c r="N83" s="19"/>
+      <c r="O83" s="19"/>
+      <c r="P83" s="19"/>
+      <c r="Q83" s="19"/>
+      <c r="R83" s="19"/>
+      <c r="S83" s="19"/>
+      <c r="T83" s="19"/>
+      <c r="U83" s="19"/>
+      <c r="V83" s="19"/>
+      <c r="W83" s="19"/>
+      <c r="X83" s="19"/>
+      <c r="Y83" s="19"/>
     </row>
     <row r="84" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="20" t="s">
+      <c r="A84" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="B84" s="20"/>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
-      <c r="J84" s="20"/>
-      <c r="K84" s="20"/>
-      <c r="L84" s="20"/>
-      <c r="M84" s="20"/>
-      <c r="N84" s="20"/>
-      <c r="O84" s="20"/>
-      <c r="P84" s="20"/>
-      <c r="Q84" s="20"/>
-      <c r="R84" s="20"/>
-      <c r="S84" s="20"/>
-      <c r="T84" s="20"/>
-      <c r="U84" s="20"/>
-      <c r="V84" s="20"/>
-      <c r="W84" s="20"/>
-      <c r="X84" s="20"/>
-      <c r="Y84" s="20"/>
+      <c r="B84" s="19"/>
+      <c r="C84" s="19"/>
+      <c r="D84" s="19"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="19"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="19"/>
+      <c r="K84" s="19"/>
+      <c r="L84" s="19"/>
+      <c r="M84" s="19"/>
+      <c r="N84" s="19"/>
+      <c r="O84" s="19"/>
+      <c r="P84" s="19"/>
+      <c r="Q84" s="19"/>
+      <c r="R84" s="19"/>
+      <c r="S84" s="19"/>
+      <c r="T84" s="19"/>
+      <c r="U84" s="19"/>
+      <c r="V84" s="19"/>
+      <c r="W84" s="19"/>
+      <c r="X84" s="19"/>
+      <c r="Y84" s="19"/>
     </row>
     <row r="85" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="22" t="s">
+      <c r="A85" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="B85" s="22"/>
-      <c r="C85" s="22"/>
-      <c r="D85" s="22"/>
-      <c r="E85" s="22"/>
-      <c r="F85" s="22"/>
-      <c r="G85" s="22"/>
-      <c r="H85" s="22"/>
-      <c r="I85" s="22"/>
-      <c r="J85" s="22"/>
-      <c r="K85" s="22"/>
-      <c r="L85" s="22"/>
-      <c r="M85" s="22"/>
-      <c r="N85" s="22"/>
-      <c r="O85" s="22"/>
-      <c r="P85" s="22"/>
-      <c r="Q85" s="22"/>
-      <c r="R85" s="22"/>
-      <c r="S85" s="22"/>
-      <c r="T85" s="22"/>
-      <c r="U85" s="22"/>
-      <c r="V85" s="22"/>
-      <c r="W85" s="22"/>
-      <c r="X85" s="22"/>
-      <c r="Y85" s="22"/>
+      <c r="B85" s="21"/>
+      <c r="C85" s="21"/>
+      <c r="D85" s="21"/>
+      <c r="E85" s="21"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="21"/>
+      <c r="H85" s="21"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="21"/>
+      <c r="K85" s="21"/>
+      <c r="L85" s="21"/>
+      <c r="M85" s="21"/>
+      <c r="N85" s="21"/>
+      <c r="O85" s="21"/>
+      <c r="P85" s="21"/>
+      <c r="Q85" s="21"/>
+      <c r="R85" s="21"/>
+      <c r="S85" s="21"/>
+      <c r="T85" s="21"/>
+      <c r="U85" s="21"/>
+      <c r="V85" s="21"/>
+      <c r="W85" s="21"/>
+      <c r="X85" s="21"/>
+      <c r="Y85" s="21"/>
     </row>
     <row r="86" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M86" s="23"/>
+      <c r="M86" s="19"/>
     </row>
     <row r="87" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M87" s="23"/>
+      <c r="M87" s="19"/>
     </row>
     <row r="88" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M88" s="23"/>
+      <c r="M88" s="19"/>
     </row>
     <row r="89" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M89" s="23"/>
+      <c r="M89" s="19"/>
     </row>
     <row r="90" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M90" s="24"/>
+      <c r="M90" s="22"/>
     </row>
     <row r="91" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M91" s="23"/>
+      <c r="M91" s="19"/>
     </row>
     <row r="92" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M92" s="23"/>
+      <c r="M92" s="19"/>
     </row>
     <row r="93" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M93" s="23"/>
+      <c r="M93" s="19"/>
     </row>
     <row r="94" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="M94" s="25"/>
+      <c r="M94" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="24">
